--- a/contenus/tab4/cap01-saisir-bon-livraison.xlsx
+++ b/contenus/tab4/cap01-saisir-bon-livraison.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +84,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00B4690E"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -102,8 +113,18 @@
         <fgColor rgb="00FBF3E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4690E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2D8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -130,11 +151,99 @@
         <color rgb="00D8D4CC"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B4690E"/>
+      </left>
+      <right style="medium">
+        <color rgb="00B4690E"/>
+      </right>
+      <top style="medium">
+        <color rgb="00B4690E"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B4690E"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00B4690E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B4690E"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00B4690E"/>
+      </right>
+      <top style="medium">
+        <color rgb="00B4690E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00B4690E"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B4690E"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00B4690E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00B4690E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00B4690E"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00B4690E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="008A8577"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +293,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -794,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1088,47 +1214,74 @@
       <c r="D20" s="18" t="n"/>
       <c r="E20" s="18" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>RÉSERVES À LA LIVRAISON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>À remplir s'il manque quelque chose, ou si un colis est abîmé. Rien d'écrit ici = marchandise acceptée telle quelle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Nom du réceptionnaire :</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Signature :</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>⚠  RÉSERVES À LA LIVRAISON — à remplir AVANT de signer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Colis manquant, carton abîmé, palette éventrée : écrivez-le ici. Rien d'écrit = marchandise acceptée telle quelle, et plus aucune réclamation possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="27" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="28" t="n"/>
+      <c r="E24" s="29" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="32" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Nom du réceptionnaire</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Date et signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="33" t="n"/>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Entreprise fictive — support pédagogique, lycée Gaston Darboux, Nîmes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A23:E25"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D3:E3"/>
